--- a/AAII_Financials/Quarterly/PVH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PVH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>PVH</t>
   </si>
@@ -656,503 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F7" s="2">
         <v>46054</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45963</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45872</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45781</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45690</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45599</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45508</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45417</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45326</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44955</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44864</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44682</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44591</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44409</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44318</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44136</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44045</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43954</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43863</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43772</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43681</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43590</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43499</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43408</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43317</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43226</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43135</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43037</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42946</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42764</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2097000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2025100</v>
+      </c>
+      <c r="F8" s="3">
         <v>2505100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2294300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2167200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1983600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2371600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2255100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2074300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1951900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2489900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2362900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2207000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2157900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2488700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2280800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2132000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2122700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2429700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2332500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2313200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2079300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2089800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2118100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1580700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1344000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2600800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2587700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2364200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2356300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2484000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>2524500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>2333700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>2314600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>2498900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>2357000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>2069900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>1989000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>2107700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>2244300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>881900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>838900</v>
+      </c>
+      <c r="F9" s="3">
         <v>1061800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1001500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>916400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>821900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>990300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>938500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>828400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>753200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>988700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1023500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>934700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>907600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1098200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1006600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>912500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>884000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1013400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>987400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>979600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>850200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>963500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1016800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>697400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>678100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1202900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1181500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1075800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1060400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1128500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>1159700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>1036700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>1023600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>1129900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>1059700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>922600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>908200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>969700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>1052700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1215100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1186200</v>
+      </c>
+      <c r="F10" s="3">
         <v>1443300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1292800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1250800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1161700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1381300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1316600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1245900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1198700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1501200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1339400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1272300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1250300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1390500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1274200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1219500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1238700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1416300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1345100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1333600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1229100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1126300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1101300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>883300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>665900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1397900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1406200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1288400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1295900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1355500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1364800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1297000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1291000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1369000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1297300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1147300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1080800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>1138000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>1191600</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1218,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1313,8 +1339,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,172 +1464,184 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>316800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F14" s="3">
         <v>20600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>21500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>45000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>492700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-34500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>53400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>15300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-6100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>18800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>39000</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>447200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>57400</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>14900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>51300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>79800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>2700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>66200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>968000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>162600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>1500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>-109000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>88900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>13200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>4700</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>29200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>2200</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>61400</v>
+      </c>
+      <c r="F15" s="3">
         <v>52200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>67100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>66400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>67700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>50500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>69700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>69800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>72100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>58700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>75200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>75500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>72300</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1610,11 +1654,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
@@ -1628,23 +1672,23 @@
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD15" s="3">
         <v>1300</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>1400</v>
       </c>
       <c r="AE15" s="3">
         <v>1300</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
+      <c r="AF15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>1300</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>8</v>
@@ -1652,11 +1696,11 @@
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>0</v>
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL15" s="3">
         <v>0</v>
@@ -1670,8 +1714,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1760,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1985100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1907200</v>
+      </c>
+      <c r="F17" s="3">
         <v>2247700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2102000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2001200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1833600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2209400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2029200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1896000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1770000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2150000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2128000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2033900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1971000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2191300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2494800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1955000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1912400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2206400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1955700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2034200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1881900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2066100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1997400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1587000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2558700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2696500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2318200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2114400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2221200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2350300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>2242200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2102300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>2070300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>2440900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>2076300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>1889400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1875800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>1954000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>2046400</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>117900</v>
+      </c>
+      <c r="F18" s="3">
         <v>257400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>192300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>166000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>150000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>162200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>225900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>178300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>181900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>339900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>234900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>173100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>186900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>297400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-214000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>177000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>210300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>223300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>376800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>279000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>197400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>23700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>120700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1214700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-95700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>269500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>249800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>135100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>133700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>282300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>231400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>244300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>58000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>280700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>180500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>113200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>153700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>197900</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,603 +2055,635 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-12200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-10500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-13500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-10600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-13200</v>
       </c>
       <c r="L20" s="3">
         <v>-10900</v>
       </c>
       <c r="M20" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="O20" s="3">
         <v>-13700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-9200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-11900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1700</v>
       </c>
       <c r="V20" s="3">
         <v>1000</v>
       </c>
       <c r="W20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>1400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>1200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>2000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>1400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>1200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>1700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>1900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>192600</v>
+      </c>
+      <c r="F21" s="3">
         <v>321600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>269400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>244600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>228200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>226200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>306200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>259000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>267200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>409500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>323800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>257800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>271100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>375700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-138600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>253900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>288300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>304400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>455800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>358300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>276100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>110700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>201800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>73200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1132300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>352500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>329500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>212700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>222100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>365000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>315600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>328500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>145900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>363300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>262300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>192100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>239800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>284300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F22" s="3">
         <v>22800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>23200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>25800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>22400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>20700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>23000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>22800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>23300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>23800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>24300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>25900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>25300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>23700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>21100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>21800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>23000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>24900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>25900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>27300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>30500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>33300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>33000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>28100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>26200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>31500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>29200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>28300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>31000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>30800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>30300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>30300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>29400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>34900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>32300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>30900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>30400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>30600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-202600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>108500</v>
+      </c>
+      <c r="F23" s="3">
         <v>229400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>160300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>111200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-349600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>196500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>167000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>154800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>187400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>336900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>207600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>119700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>176800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>275800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-232800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>156700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>188500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>199400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>352600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>252700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>168000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>88600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-33800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1239600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-125700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>241700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>222800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>105200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>104500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>252900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>202300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>215900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>25100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>249800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>150800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>84500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>125000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>168700</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-99700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F24" s="3">
         <v>387700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>156100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-113000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-304800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>39300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>35100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-3200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>36000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>65100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>46000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>25500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>40800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>137100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-46100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>41400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>55400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-191400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>72900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>70900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>68300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>49900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>19100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>17900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-142400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-57200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>32800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>29700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>23600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-29200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>10300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>37600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>37000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>90900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>11100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>31400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>14400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>24500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2801,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>88000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-158300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>224200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-44800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>157200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>131900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>158000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>151400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>271800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>161600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>94200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>136000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>138700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-186700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>115300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>133100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>390800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>279700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>181800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>99700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-58100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>69500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-51700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1097200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-68500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>208900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>193100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>81600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>133700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>242600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>164700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>178900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-65800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>238700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>119400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>70100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>100500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>126100</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>88000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-158300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>224200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-44800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>157200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>131900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>158000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>151400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>271800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>161600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>94200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>136000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>138700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-186700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>115300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>133100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>390800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>279700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>181900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>99900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>69800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-51400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1096800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-67400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>209200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>193500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>82000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>134000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>243100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>165200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>179400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-65200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>239200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>119700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>70400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>100700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>126200</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3176,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3133,11 +3253,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3151,26 +3271,26 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>24700</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
+      <c r="AH29" s="3">
+        <v>24700</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>173700</v>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
+      <c r="AL29" s="3">
+        <v>173700</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3181,8 +3301,14 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3426,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3551,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F32" s="3">
         <v>12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>12200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>10500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>13500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>10600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>10900</v>
-      </c>
-      <c r="K32" s="3">
-        <v>13200</v>
       </c>
       <c r="L32" s="3">
         <v>10900</v>
       </c>
       <c r="M32" s="3">
+        <v>13200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>10900</v>
+      </c>
+      <c r="O32" s="3">
         <v>13700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>9200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>11900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1700</v>
       </c>
       <c r="V32" s="3">
         <v>-1000</v>
       </c>
       <c r="W32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>88000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-158300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>224200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-44800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>157200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>131900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>158000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>151400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>271800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>161600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>94200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>136000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>138700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-186700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>115300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>133100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>390800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>279700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>181900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>99900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>69800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-51400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1096800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-67400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>209200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>193500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>82000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>158700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>243100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>165200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>179400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>108500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>239200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>119700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>70400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>100700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>126200</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3926,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>88000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-158300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>224200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-44800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>157200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>131900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>158000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>151400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>271800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>161600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>94200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>136000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>138700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-186700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>115300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>133100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>390800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>279700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>181900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>99900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>69800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-51400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1096800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-67400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>209200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>193500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>82000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>158700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>243100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>165200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>179400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>108500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>239200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>119700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>70400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>100700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>126200</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F38" s="2">
         <v>46054</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45963</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45872</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45781</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45690</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45599</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45508</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45417</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45326</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44955</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44864</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44682</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44591</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44409</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44318</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44136</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44045</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43954</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43863</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43772</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43681</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43590</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43499</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43408</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43317</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43226</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43135</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43037</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42946</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42764</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4230,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,127 +4275,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>965900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>592500</v>
+      </c>
+      <c r="F41" s="3">
         <v>701500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>158200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>248800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>191000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>748000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>559600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>610000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>376200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>707600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>357600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>372800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>373800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>550700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>457000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>699300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>748700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1242500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1298700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1152600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>913200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1651400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1460000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1394300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>800700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>503400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>555200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>433500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>494300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>452000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>398500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>431100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>434500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>493900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>612300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>559400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>490900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>730100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>662400</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4343,841 +4521,889 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>941600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>918700</v>
+      </c>
+      <c r="F43" s="3">
         <v>1017900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1120200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>919200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>872800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>876300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>999000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>906900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>835000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>807200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1062600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>910000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>928300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>945200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1002300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>837500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>872500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>765300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>936600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>847200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>883300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>666600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>818700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>596200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>566900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>765100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>998800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>808900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>876000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>803800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>965600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>731600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>812300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>696400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>857100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>672600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>712500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>641400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>788400</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1738200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1510200</v>
+      </c>
+      <c r="F44" s="3">
         <v>1583500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1664000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1791000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1596000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1508700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1608200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1582800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1346800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1419700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1476900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1795500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1718100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1802600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1821200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1689900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1389700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1348500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1379600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1421300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1450900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1417100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1483500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1642200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1561200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1615700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1768100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1862100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1608400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1732400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>1686900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>1731000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>1524900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>1591300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>1466200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>1498600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>1253800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>1317900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>1258300</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>85700</v>
+      </c>
+      <c r="F45" s="3">
         <v>83300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>95100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>81900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>113400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>144100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>89500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>80100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>90100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>87500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>241500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>79800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>78600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>281900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>374200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>357700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>354100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>297400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>244000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>333200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>235600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>208600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>205700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>214100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>259500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>510000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>260000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>294100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>274700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>250400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>256800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>272300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>269900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>249200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>208500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>204900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>198000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>190200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>239000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3982700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3375300</v>
+      </c>
+      <c r="F46" s="3">
         <v>3605200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3275600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3299300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3033600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3487600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3478200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3414400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2911900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3259700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3347100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3414100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3353200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3580400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3654700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3584400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3365000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3653700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3858900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3754300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3483000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3943700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3967900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3846800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3188300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3394200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3582100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3398600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3253400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3238600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>3307800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>3166000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>3041600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>3030800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>3144100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>2935500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>2655200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>2879600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>2948100</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>214300</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
+      <c r="F47" s="3">
+        <v>214300</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>198200</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>198200</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>215500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>198000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>195800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>191500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>190200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>175400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>164900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>158900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>165300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>157300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>154700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>159100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>164000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>153100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>144100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>142100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>176300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>148400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>146600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>208500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>207100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>198000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>201300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>198600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>208400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>186300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>191000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>182000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>180000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AQ47" s="3">
         <v>119200</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2404600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2461100</v>
+      </c>
+      <c r="F48" s="3">
         <v>2535200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2533600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2583100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1963200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1898500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1986500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2030900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2081900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2076400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2082600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2167200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2167800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2199700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2021700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2072300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2175800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2255100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2329200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2365700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2403500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2507500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2566900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2671600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2614500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2702600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>2642800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>2634100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>2568300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>984500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>923700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>881300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>873500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>899800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>821200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>805800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>751600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>759900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>730200</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4615300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5098300</v>
+      </c>
+      <c r="F49" s="3">
         <v>5118100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5045200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5056100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4997100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>5281000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>5406300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5424500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>5404800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>5419500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>5362600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>5586500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>5588700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>5608900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>5358400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>5897500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>5998100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>6135900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>6270300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>6323800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>6455500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>6472500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>6345000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>6369200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>6144400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>7158300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>7458100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>7461100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>7149700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>7239700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>7230200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>7284600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>7434900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>7561300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>7336000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>7348700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>7163400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>7079900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>7154800</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5521,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5646,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>319400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>310200</v>
+      </c>
+      <c r="F52" s="3">
         <v>109200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>309400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>312700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>311000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>130900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>334100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>339200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>353800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>168000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>157100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>154700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>159300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>189100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>195700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>203200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>191500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>186800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>200300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>198800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>200500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>205800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>224300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>220800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>204900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>199600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>187800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>180500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>175100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>193800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>171200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>164500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>166000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>185400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>170600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>172900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>160100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>168500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>116300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5896,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11416700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>11341600</v>
+      </c>
+      <c r="F54" s="3">
         <v>11681000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11421200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11627600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>10672400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11033200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11241300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11237700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10788700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11172900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11167100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>11542400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>11491200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>11768300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>11405900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>11922300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>11889300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>12396800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>12816000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>12797300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>12701600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>13293500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>13257200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>13252500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>12294200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>13631000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>14019200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>13820900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>13355000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>11863700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>11830900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>11697700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>11714600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>11885700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>11658200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>11453900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>10912300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>11067900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>11068600</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +6070,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,722 +6115,760 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1298800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>906700</v>
+      </c>
+      <c r="F57" s="3">
         <v>1146900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1041500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1288000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>991000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1151000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1137400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1200900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>863000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1073400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>999100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1242900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1063000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1327400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1314300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1359000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1062200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1220800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1051300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1069500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1023800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1124200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1134400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1048200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>783900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>882800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>780500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>930200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>696200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>924200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>752500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>922600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>670500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>889800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>681300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>767100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>546700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>682600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>496500</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>360800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>352500</v>
+      </c>
+      <c r="F58" s="3">
         <v>361700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>352800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>342400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>921200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>803100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>804500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>822000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>316100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>870500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1002700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1032700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>471500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>158100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>135300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>50400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>51700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>45600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>60600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>48900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>40200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>41100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>44000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>85400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>335700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>68000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>433500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>229100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>335400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>12800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>276700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>85400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>254500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>19500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>207500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>18000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>42500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>19100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AQ58" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>62500</v>
+      </c>
+      <c r="F59" s="3">
         <v>80100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>113100</v>
       </c>
-      <c r="F59" s="3">
-        <v>151500</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>94800</v>
+      </c>
+      <c r="I59" s="3">
         <v>136200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>56800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>48700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>67500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>68500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>79400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>49000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>100500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>89300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1282000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1255900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1247100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1314800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1521100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1547400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1413000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1324500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1417100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1389500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1392500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1202000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1410300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1338700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1268400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1175000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>956900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>869400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>827700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>802100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>962300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>837500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>848100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>789000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>863100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>839100</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2013000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2376200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2235100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2410300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2730500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2741800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2694700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2760100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1877400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2771500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2845500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3123600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2396200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2767500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2705500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2656500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2428700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2787500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2659300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2531400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2388500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2582400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2567900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2526100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2321600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2361100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2552700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2427700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2206600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1893900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>1898600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>1835700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>1727100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>1871600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>1726300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>1633200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>1378200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>1564800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>1356400</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3803900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3873500</v>
+      </c>
+      <c r="F61" s="3">
         <v>3939900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3907200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3947600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2813300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2593900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2712800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2745300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3255900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2673100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2666900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2767500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3329000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2177000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2109100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2155500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2216500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2317600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2605200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2782500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3018200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>3513700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3464100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>3498300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2854200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2703800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2749500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2753600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2770400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2819400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2878300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>2893500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>3013200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>3061300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>3182700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>3185700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>3157100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>3197300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>3303100</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>242500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>250100</v>
+      </c>
+      <c r="F62" s="3">
         <v>260600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>249800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>245100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>214500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>216700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>205600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>203900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>241600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>253900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>267300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>281600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>282700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1811100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1768500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1903900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1975600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2002900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2379800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2450600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2459100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2470500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2552000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2647300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2607400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2756600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2732800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>2768500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>2616700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1322400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1372300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1402100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1408200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1414400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>1496800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>1536700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>1498600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>1499300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>1613600</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6986,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +7111,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7236,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6624700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6446900</v>
+      </c>
+      <c r="F66" s="3">
         <v>6888700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6542200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6761000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6054200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5892700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5953100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6045900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5729500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6054000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6112800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6504800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>6364800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>6755600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>6583100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>6715900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>6620800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>7108000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>7644300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>7764500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>7862200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>8563200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>8581000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8669000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>7780800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>7819500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>8034100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>7949200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>7593500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>6035900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>6149700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>6132300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>6150000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>6349300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>6408400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>6358700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>6037300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>6263400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>6274300</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7410,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7531,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7656,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7781,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7906,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5996600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6099500</v>
+      </c>
+      <c r="F72" s="3">
         <v>6015000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>6173300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>6172700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>5948500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5997200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5840000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>5712400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>5554400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>5407300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>5137800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4978500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4886700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4753100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>4616800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>4806000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>4693300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>4562800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>4172000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3895000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>3713100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>3613200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>3670900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>3601100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>3652500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>4753000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>4820400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>4614000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>4423300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>4350100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>4191400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>3951100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>3788800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>3625200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>3514700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>3278400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>3161700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>3098000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>2997300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +8156,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8281,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8406,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4792000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4894700</v>
+      </c>
+      <c r="F76" s="3">
         <v>4792300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4879000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4866600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4618200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5140500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5288200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5191800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5059200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5118900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5054300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5037600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5126400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5012700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4822800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5206400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5268500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>5288800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5171700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>5032800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4839400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4730300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4676200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4583500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4513400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5811500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5985100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5871700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5761500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>5827800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>5681200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>5565400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>5564600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>5536400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>5249800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>5095200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>4875000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>4804500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>4794300</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8656,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F80" s="2">
         <v>46054</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45963</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45872</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45781</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45690</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45599</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45508</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45417</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45326</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44955</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44864</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44682</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44591</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44409</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44318</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44136</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44045</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43954</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43863</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43772</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43681</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43590</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43499</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43408</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43317</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43226</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43135</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43037</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42946</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42764</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>88000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-158300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>224200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-44800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>157200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>131900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>158000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>151400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>271800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>161600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>94200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>136000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>138700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-186700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>115300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>133100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>390800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>279700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>181900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>99900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>69800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-51400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1096800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-67400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>209200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>193500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>82000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>158700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>243100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>165200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>179400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>108500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>239200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>119700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>70400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>100700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>126200</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8960,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>66400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>67700</v>
+      </c>
+      <c r="F83" s="3">
         <v>28000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>69700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>69800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>72100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>35600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>75200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>75500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>72300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>33500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>73100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>75400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>76800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>76200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>73100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>75400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>76800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>80100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>77300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>78300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>77600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>85600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>80200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>78900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>81100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>87300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>81600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>78400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>76500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>86800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>81800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>83000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>83200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>85900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>81200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>80600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>77200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>84200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>84400</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9206,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9331,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9456,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9581,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9706,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>382900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="F89" s="3">
         <v>583200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-44500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>213100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-71400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>486500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>28700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>292400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-66700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>657700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>115500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>271600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-75400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>314900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-112600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>140300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-303400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>488000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>251000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>521300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-189100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>270700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>179000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>390800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-142800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>588500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>113900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>391100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-73200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>547600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>436600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-125700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>456700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>40200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>247800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>-44900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>378400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>167700</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9880,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-43500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-40600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-31200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-26700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-43300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-40000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-36600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-38800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-81400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-47400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-58000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-57900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-95300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-86100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-56300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-52400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-97200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-60500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-61100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-49100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-67900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-51100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-51200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-56400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-112100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-82600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-73800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-76700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-109700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-104900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-88200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-76700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-122900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-79200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-87600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-68400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-83600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-60200</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +10126,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10251,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-39800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-41300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-31000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-28000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-37100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-28600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-30800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-41200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>80200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-47900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-57800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-59600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-87200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-37600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-57100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-97200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>162400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-61100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-49100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-67900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-52700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-51200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>112700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-137300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-85200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-206700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-76700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-109700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-104900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-88200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-92600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-185600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-93700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-88400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-91400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-115200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-95200</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,68 +10425,70 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="E96" s="3">
         <v>1800</v>
       </c>
       <c r="F96" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G96" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H96" s="3">
         <v>2000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>2200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>2100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>2100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>2200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>2300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>2300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>2400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>2400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-2500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-2600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-2600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-2700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10036,52 +10502,58 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-2900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10671,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10796,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,361 +10921,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-6500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-5700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-130600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-462900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-250400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-49200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-28900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-221900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-391000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-74600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-217300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-38900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-143200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-29600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-143400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-112000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-423500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-261400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-214000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-499600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-53400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>218700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>336400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-502600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>94800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-242100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>198300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-385200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>78900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-338200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>166000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-443900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>119500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-89500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-94300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-192800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-145500</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-10600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>3100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-8200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>18300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-12900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-8700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-21300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>18300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-12900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-8700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-21300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-23500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-5900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-6800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>12900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>35300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-13600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>15900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>11700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>3900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>-6300</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>373400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-109000</v>
+      </c>
+      <c r="F102" s="3">
         <v>543300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-90600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>57800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-557000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>188400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-50400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>233800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-331400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>350000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-15200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-176900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>93700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-242300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-49400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-493800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-56200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>146100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>239400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-738200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>191400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>65700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>593600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>297300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>121700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-60800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>42300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>53500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-32600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-59400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-118400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>52900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>68500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-239200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>67700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>-79300</v>
       </c>
     </row>
